--- a/docs/heatfix-google-business-profile.xlsx
+++ b/docs/heatfix-google-business-profile.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Google Business Profile — Heat Fix Mcr Limited</t>
+          <t>Google Business Profile — HeatFix Mcr Limited</t>
         </is>
       </c>
     </row>
@@ -758,14 +758,21 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>•  Yell has him as 'HeatFix MCr Ltd'; the site and the logo say 'Heat Fix Mcr Limited'. Pick one and use it</t>
+          <t>•  Yell has him as 'HeatFix MCr Ltd', the site says 'HeatFix Mcr Limited'. Same word, different ending —</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   everywhere — Google cross-checks the name against other listings, and a mismatch slows verification.</t>
+          <t xml:space="preserve">   worth making Yell match, because Google cross-checks the name against other listings and a mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   slows verification down.</t>
         </is>
       </c>
     </row>
@@ -796,7 +803,7 @@
       </c>
       <c r="B1" s="7" t="inlineStr">
         <is>
-          <t>Heat Fix Mcr Limited</t>
+          <t>HeatFix Mcr Limited</t>
         </is>
       </c>
       <c r="C1" s="7" t="inlineStr">
@@ -830,7 +837,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Heat Fix Mcr Limited</t>
+          <t>HeatFix Mcr Limited</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -1127,12 +1134,12 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Heat Fix Mcr Limited is Mohammad Ejaz, a Gas Safe registered domestic gas engineer working across Manchester and Stockport. Boiler installation, repair and servicing, unvented hot water cylinders, gas cookers, hobs and fires, bathrooms, showers, radiators and emergency plumbing. One engineer from quote to clean-up, a written price before any work starts and no call-out fee to come and look. Landlord gas safety certificates issued the same visit. Gas Safe registration 627019.</t>
+          <t>HeatFix Mcr Limited is Mohammad Ejaz, a Gas Safe registered domestic gas engineer working across Manchester and Stockport. Boiler installation, repair and servicing, unvented hot water cylinders, gas cookers, hobs and fires, bathrooms, showers, radiators and emergency plumbing. One engineer from quote to clean-up, a written price before any work starts and no call-out fee to come and look. Landlord gas safety certificates issued the same visit. Gas Safe registration 627019.</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>750 characters max. This is 479.</t>
+          <t>750 characters max. This is 478.</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1448,7 @@
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>Heat Fix Mcr Limited</t>
+          <t>HeatFix Mcr Limited</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr"/>
@@ -1518,7 +1525,7 @@
       </c>
       <c r="W2" s="14" t="inlineStr">
         <is>
-          <t>Heat Fix Mcr Limited is Mohammad Ejaz, a Gas Safe registered domestic gas engineer working across Manchester and Stockport. Boiler installation, repair and servicing, unvented hot water cylinders, gas cookers, hobs and fires, bathrooms, showers, radiators and emergency plumbing. One engineer from quote to clean-up, a written price before any work starts and no call-out fee to come and look. Landlord gas safety certificates issued the same visit. Gas Safe registration 627019.</t>
+          <t>HeatFix Mcr Limited is Mohammad Ejaz, a Gas Safe registered domestic gas engineer working across Manchester and Stockport. Boiler installation, repair and servicing, unvented hot water cylinders, gas cookers, hobs and fires, bathrooms, showers, radiators and emergency plumbing. One engineer from quote to clean-up, a written price before any work starts and no call-out fee to come and look. Landlord gas safety certificates issued the same visit. Gas Safe registration 627019.</t>
         </is>
       </c>
       <c r="X2" s="16" t="inlineStr"/>
@@ -2204,7 +2211,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Heat Fix Mcr Limited</t>
+          <t>HeatFix Mcr Limited</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2303,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Heat Fix Mcr Limited is Mohammad Ejaz, a Gas Safe registered domestic gas engineer working across Manchester and Stockport. Boiler installation, repair and servicing, unvented hot water cylinders, gas cookers, hobs and fires, bathrooms, showers, radiators and emergency plumbing. One engineer from quote to clean-up, a written price before any work starts and no call-out fee to come and look. Landlord gas safety certificates issued the same visit. Gas Safe registration 627019.</t>
+          <t>HeatFix Mcr Limited is Mohammad Ejaz, a Gas Safe registered domestic gas engineer working across Manchester and Stockport. Boiler installation, repair and servicing, unvented hot water cylinders, gas cookers, hobs and fires, bathrooms, showers, radiators and emergency plumbing. One engineer from quote to clean-up, a written price before any work starts and no call-out fee to come and look. Landlord gas safety certificates issued the same visit. Gas Safe registration 627019.</t>
         </is>
       </c>
     </row>
